--- a/data/trans_orig/P16A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486608</t>
+          <t>486368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493156</t>
+          <t>493152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441586</t>
+          <t>441467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457227</t>
+          <t>457544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930931</t>
+          <t>931773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948916</t>
+          <t>948461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41277</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64432</t>
+          <t>62941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>703878</t>
+          <t>704324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>722375</t>
+          <t>722323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584217</t>
+          <t>585453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606657</t>
+          <t>606926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1296550</t>
+          <t>1298041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1324395</t>
+          <t>1325526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41408</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70422</t>
+          <t>70216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>55883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>89883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610989</t>
+          <t>610420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627712</t>
+          <t>627358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>619528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648336</t>
+          <t>647964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237677</t>
+          <t>1238529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1271474</t>
+          <t>1272529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80932</t>
+          <t>78838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120681</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478656</t>
+          <t>478718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500056</t>
+          <t>500344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>430147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459588</t>
+          <t>460708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>914108</t>
+          <t>916691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>953857</t>
+          <t>955951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92031</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>88676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124888</t>
+          <t>125868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>344468</t>
+          <t>345260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>365581</t>
+          <t>366077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>311955</t>
+          <t>311217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343751</t>
+          <t>344064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665808</t>
+          <t>664828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>703021</t>
+          <t>702020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20374</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40396</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>55215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83852</t>
+          <t>83053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82332</t>
+          <t>82964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116039</t>
+          <t>116487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252187</t>
+          <t>253300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272209</t>
+          <t>272305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259082</t>
+          <t>259881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286729</t>
+          <t>287719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519478</t>
+          <t>519030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>553185</t>
+          <t>552553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48150</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>78009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114863</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>167458</t>
+          <t>167046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187497</t>
+          <t>187291</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>256150</t>
+          <t>255899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285758</t>
+          <t>284673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428928</t>
+          <t>429132</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>466639</t>
+          <t>465491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188322</t>
+          <t>186644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>339971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>413853</t>
+          <t>408540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495709</t>
+          <t>499543</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>588787</t>
+          <t>582131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3088221</t>
+          <t>3089899</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3138565</t>
+          <t>3138832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2965344</t>
+          <t>2970657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3037902</t>
+          <t>3039226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6066954</t>
+          <t>6073610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6160032</t>
+          <t>6156198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441174</t>
+          <t>441343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451497</t>
+          <t>451502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408433</t>
+          <t>408670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423505</t>
+          <t>423270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>856006</t>
+          <t>856163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873065</t>
+          <t>873603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39152</t>
+          <t>41860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>46623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>79457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>647935</t>
+          <t>645227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>670413</t>
+          <t>669511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>562353</t>
+          <t>563632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587497</t>
+          <t>587570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1219050</t>
+          <t>1217885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1251624</t>
+          <t>1251743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>55631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67892</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101480</t>
+          <t>102482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103552</t>
+          <t>103111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148779</t>
+          <t>147121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626920</t>
+          <t>626232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654930</t>
+          <t>654600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609370</t>
+          <t>608368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642958</t>
+          <t>642320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1243933</t>
+          <t>1245591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289160</t>
+          <t>1289601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55798</t>
+          <t>56564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85515</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122654</t>
+          <t>123850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120228</t>
+          <t>122291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168332</t>
+          <t>170650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558819</t>
+          <t>558053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585572</t>
+          <t>584520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>493545</t>
+          <t>492349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530684</t>
+          <t>530782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1062484</t>
+          <t>1060166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1110588</t>
+          <t>1108525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>59953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>87393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>121300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>129941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176757</t>
+          <t>172898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369720</t>
+          <t>369476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395221</t>
+          <t>395738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324289</t>
+          <t>326500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360249</t>
+          <t>360407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700472</t>
+          <t>704331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>748417</t>
+          <t>747288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>74943</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107302</t>
+          <t>109759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102990</t>
+          <t>105110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146659</t>
+          <t>144740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262521</t>
+          <t>261261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287304</t>
+          <t>286902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246694</t>
+          <t>244237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279160</t>
+          <t>279053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517123</t>
+          <t>519042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560792</t>
+          <t>558672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>105976</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146417</t>
+          <t>145607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136791</t>
+          <t>139285</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184907</t>
+          <t>185322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200757</t>
+          <t>200038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225373</t>
+          <t>224565</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>242562</t>
+          <t>243372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>281639</t>
+          <t>283003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>453923</t>
+          <t>453508</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>502039</t>
+          <t>499545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198997</t>
+          <t>198349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261076</t>
+          <t>262165</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>513093</t>
+          <t>507726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>597912</t>
+          <t>595880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>728374</t>
+          <t>732170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>840686</t>
+          <t>840872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3165703</t>
+          <t>3164614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3227782</t>
+          <t>3228430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2960397</t>
+          <t>2962429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3045216</t>
+          <t>3050583</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6144402</t>
+          <t>6144216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6256714</t>
+          <t>6252918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408673</t>
+          <t>409170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418403</t>
+          <t>418406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375516</t>
+          <t>375249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389362</t>
+          <t>389390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789059</t>
+          <t>789177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805691</t>
+          <t>805400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>46994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>567661</t>
+          <t>567775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582517</t>
+          <t>582610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533380</t>
+          <t>533836</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>550341</t>
+          <t>551290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1106804</t>
+          <t>1107046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1129848</t>
+          <t>1129216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>47407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74002</t>
+          <t>77496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>77621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113799</t>
+          <t>113598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621504</t>
+          <t>620394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645576</t>
+          <t>644353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>587384</t>
+          <t>583890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>614989</t>
+          <t>613979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216684</t>
+          <t>1216885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255151</t>
+          <t>1252862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60377</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120290</t>
+          <t>118778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121150</t>
+          <t>122244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168673</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>585671</t>
+          <t>587430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613794</t>
+          <t>612703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528787</t>
+          <t>530299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569021</t>
+          <t>567493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1126452</t>
+          <t>1124503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1173975</t>
+          <t>1172881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30167</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>57937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>110834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153830</t>
+          <t>150226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148175</t>
+          <t>149417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196754</t>
+          <t>200245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>420061</t>
+          <t>419981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447751</t>
+          <t>446885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>343019</t>
+          <t>346623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>384778</t>
+          <t>386015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778013</t>
+          <t>774522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>826592</t>
+          <t>825350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>131249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126243</t>
+          <t>127151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170307</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288002</t>
+          <t>288508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309389</t>
+          <t>309044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245822</t>
+          <t>246513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>282292</t>
+          <t>283872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541785</t>
+          <t>541908</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>585849</t>
+          <t>584941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84492</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124081</t>
+          <t>125550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121243</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>163695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208550</t>
+          <t>207420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>229024</t>
+          <t>227674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276088</t>
+          <t>274619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315677</t>
+          <t>316173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491702</t>
+          <t>493472</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>535924</t>
+          <t>537626</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187163</t>
+          <t>184534</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>243107</t>
+          <t>240749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>495516</t>
+          <t>494082</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>583035</t>
+          <t>583729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>696759</t>
+          <t>699388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>802928</t>
+          <t>800588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3151243</t>
+          <t>3153601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3207187</t>
+          <t>3209816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2961507</t>
+          <t>2960813</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3049026</t>
+          <t>3050460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6135964</t>
+          <t>6138304</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6242133</t>
+          <t>6239504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>317</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376527</t>
+          <t>374350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399537</t>
+          <t>399670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285329</t>
+          <t>285313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306927</t>
+          <t>307197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676621</t>
+          <t>674958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704138</t>
+          <t>703840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33044</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43850</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404103</t>
+          <t>406134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419981</t>
+          <t>420235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479049</t>
+          <t>479311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500861</t>
+          <t>500777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891790</t>
+          <t>892342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917651</t>
+          <t>917116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43500</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65957</t>
+          <t>65455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>67946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102065</t>
+          <t>101266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492838</t>
+          <t>493595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515509</t>
+          <t>515385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526045</t>
+          <t>526547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>553068</t>
+          <t>554816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1026275</t>
+          <t>1027074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1062171</t>
+          <t>1060394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92411</t>
+          <t>92820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86256</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126496</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100454</t>
+          <t>100968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206851</t>
+          <t>207135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>795375</t>
+          <t>794966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862255</t>
+          <t>861830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>586385</t>
+          <t>588174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626625</t>
+          <t>627471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393816</t>
+          <t>1393532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1500213</t>
+          <t>1499699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83606</t>
+          <t>82292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>123048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152502</t>
+          <t>154551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183530</t>
+          <t>183783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225035</t>
+          <t>226382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>477628</t>
+          <t>478942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507109</t>
+          <t>506442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395403</t>
+          <t>393354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424848</t>
+          <t>424857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>884104</t>
+          <t>882757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925609</t>
+          <t>925356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176734</t>
+          <t>176921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>79752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209206</t>
+          <t>208967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312923</t>
+          <t>313334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332145</t>
+          <t>333682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>431634</t>
+          <t>431447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>560971</t>
+          <t>559975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>767327</t>
+          <t>767566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>889270</t>
+          <t>896781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55079</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143709</t>
+          <t>145164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171762</t>
+          <t>172816</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206899</t>
+          <t>205332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>241399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206475</t>
+          <t>206494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227680</t>
+          <t>228836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254069</t>
+          <t>253015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282122</t>
+          <t>280667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>466457</t>
+          <t>467191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>501691</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>225782</t>
+          <t>222400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>324905</t>
+          <t>320799</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>478497</t>
+          <t>490632</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>656282</t>
+          <t>660644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775592</t>
+          <t>760517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>964118</t>
+          <t>961645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3134912</t>
+          <t>3139018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3234035</t>
+          <t>3237417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3055998</t>
+          <t>3051636</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3233783</t>
+          <t>3221648</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6207979</t>
+          <t>6210452</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6396505</t>
+          <t>6411580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486368</t>
+          <t>485686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493152</t>
+          <t>493160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441467</t>
+          <t>440252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457544</t>
+          <t>457052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>931773</t>
+          <t>931079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948461</t>
+          <t>948518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31165</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>64814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>704324</t>
+          <t>704206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>722323</t>
+          <t>721897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>585453</t>
+          <t>585008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606926</t>
+          <t>606840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1298041</t>
+          <t>1296168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1325526</t>
+          <t>1324082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>40469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70216</t>
+          <t>69355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55883</t>
+          <t>56574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89883</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610420</t>
+          <t>610640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627358</t>
+          <t>627371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619528</t>
+          <t>620389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647964</t>
+          <t>649275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1238529</t>
+          <t>1239042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1272529</t>
+          <t>1271838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>56364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>85606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118098</t>
+          <t>118754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478718</t>
+          <t>477524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500344</t>
+          <t>499685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>430147</t>
+          <t>430036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460708</t>
+          <t>459278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>916691</t>
+          <t>916035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>955951</t>
+          <t>953360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125868</t>
+          <t>124145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345260</t>
+          <t>344689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366077</t>
+          <t>365714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>311217</t>
+          <t>311860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344064</t>
+          <t>343201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664828</t>
+          <t>666551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702020</t>
+          <t>702862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55215</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83053</t>
+          <t>83663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82964</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116487</t>
+          <t>116181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253300</t>
+          <t>252670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272305</t>
+          <t>272083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259881</t>
+          <t>259271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287719</t>
+          <t>287459</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519030</t>
+          <t>519336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552553</t>
+          <t>554059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42837</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78009</t>
+          <t>79547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>77113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114659</t>
+          <t>114635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>167046</t>
+          <t>167660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187291</t>
+          <t>187688</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>255899</t>
+          <t>254361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284673</t>
+          <t>284914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>429132</t>
+          <t>429156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465491</t>
+          <t>466678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>339971</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>408540</t>
+          <t>412231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>499543</t>
+          <t>495382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>582131</t>
+          <t>586238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3089899</t>
+          <t>3089072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3138832</t>
+          <t>3140880</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2970657</t>
+          <t>2966966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3039226</t>
+          <t>3036436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6073610</t>
+          <t>6069503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6156198</t>
+          <t>6160359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441343</t>
+          <t>441494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451502</t>
+          <t>451361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408670</t>
+          <t>409094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423270</t>
+          <t>424263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>856163</t>
+          <t>855832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873603</t>
+          <t>872657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46623</t>
+          <t>48170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45599</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79457</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>645227</t>
+          <t>647437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>669511</t>
+          <t>670598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>563632</t>
+          <t>562085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587570</t>
+          <t>586397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1217885</t>
+          <t>1219541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1251743</t>
+          <t>1252064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55631</t>
+          <t>54329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68530</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102482</t>
+          <t>102434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103111</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147121</t>
+          <t>145085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626232</t>
+          <t>627534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654600</t>
+          <t>655111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>608416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642320</t>
+          <t>642648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1245591</t>
+          <t>1247627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289601</t>
+          <t>1291680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56564</t>
+          <t>56258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85417</t>
+          <t>85228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123850</t>
+          <t>124256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122291</t>
+          <t>123234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170650</t>
+          <t>168862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558053</t>
+          <t>558359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>584520</t>
+          <t>584567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>492349</t>
+          <t>491943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530782</t>
+          <t>530971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1060166</t>
+          <t>1061954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1108525</t>
+          <t>1107582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59953</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121300</t>
+          <t>124428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129941</t>
+          <t>128055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172898</t>
+          <t>173647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369476</t>
+          <t>371161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395738</t>
+          <t>396715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326500</t>
+          <t>323372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360407</t>
+          <t>358092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704331</t>
+          <t>703582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>747288</t>
+          <t>749174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74943</t>
+          <t>74755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109759</t>
+          <t>108454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105110</t>
+          <t>104383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144740</t>
+          <t>146021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261261</t>
+          <t>262809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286902</t>
+          <t>286873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244237</t>
+          <t>245542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279053</t>
+          <t>279241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519042</t>
+          <t>517761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>558672</t>
+          <t>559399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49813</t>
+          <t>49317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>106733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145607</t>
+          <t>146818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139285</t>
+          <t>137403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185322</t>
+          <t>183668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200038</t>
+          <t>200534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224565</t>
+          <t>224754</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>243372</t>
+          <t>242161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>283003</t>
+          <t>282246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>453508</t>
+          <t>455162</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>499545</t>
+          <t>501427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198349</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>262165</t>
+          <t>259956</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>507726</t>
+          <t>515873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>595880</t>
+          <t>602809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>732170</t>
+          <t>727951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>840872</t>
+          <t>834702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3164614</t>
+          <t>3166823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3228430</t>
+          <t>3231509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2962429</t>
+          <t>2955500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3050583</t>
+          <t>3042436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6144216</t>
+          <t>6150386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6252918</t>
+          <t>6257137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409170</t>
+          <t>408297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418406</t>
+          <t>418407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375249</t>
+          <t>374706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389390</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789177</t>
+          <t>789304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805400</t>
+          <t>805719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46994</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>567775</t>
+          <t>568644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582610</t>
+          <t>582627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533836</t>
+          <t>534173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>551290</t>
+          <t>550562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1107046</t>
+          <t>1108416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1129216</t>
+          <t>1130034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48703</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>47037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>76146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113598</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620394</t>
+          <t>619402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644353</t>
+          <t>644422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>583890</t>
+          <t>586428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613979</t>
+          <t>614349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216885</t>
+          <t>1216677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252862</t>
+          <t>1254337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81584</t>
+          <t>81273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118778</t>
+          <t>118822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122244</t>
+          <t>121002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>166843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>587430</t>
+          <t>586718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612703</t>
+          <t>613193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530299</t>
+          <t>530255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>567493</t>
+          <t>567804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1124503</t>
+          <t>1128282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1172881</t>
+          <t>1174123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57937</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110834</t>
+          <t>110078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150226</t>
+          <t>151820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149417</t>
+          <t>149229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200245</t>
+          <t>200195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419981</t>
+          <t>420410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>446885</t>
+          <t>447302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346623</t>
+          <t>345029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>386015</t>
+          <t>386771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774522</t>
+          <t>774572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>825350</t>
+          <t>825538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93890</t>
+          <t>95484</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131249</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127151</t>
+          <t>125918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170184</t>
+          <t>169691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288508</t>
+          <t>287783</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309044</t>
+          <t>309769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246513</t>
+          <t>244854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>283872</t>
+          <t>282278</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541908</t>
+          <t>542401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584941</t>
+          <t>586174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49578</t>
+          <t>49181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>84350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125550</t>
+          <t>125482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>121353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163695</t>
+          <t>166430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207420</t>
+          <t>207817</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227674</t>
+          <t>228348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274619</t>
+          <t>274687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316173</t>
+          <t>315819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>493472</t>
+          <t>490737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537626</t>
+          <t>535814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>186862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240749</t>
+          <t>243370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>494082</t>
+          <t>500061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>583729</t>
+          <t>586337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>699388</t>
+          <t>696469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>800588</t>
+          <t>802855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3153601</t>
+          <t>3150980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3209816</t>
+          <t>3207488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2960813</t>
+          <t>2958205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3050460</t>
+          <t>3044481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6138304</t>
+          <t>6136037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6239504</t>
+          <t>6242423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>394661</t>
+          <t>401442</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374350</t>
+          <t>388319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399670</t>
+          <t>406544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>298924</t>
+          <t>347374</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285313</t>
+          <t>331498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307197</t>
+          <t>356180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>693585</t>
+          <t>748816</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674958</t>
+          <t>732032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703840</t>
+          <t>759762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32782</t>
+          <t>32465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415114</t>
+          <t>465878</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406134</t>
+          <t>456151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420235</t>
+          <t>471711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>491000</t>
+          <t>480245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479311</t>
+          <t>469268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500777</t>
+          <t>488424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>906114</t>
+          <t>946123</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>892342</t>
+          <t>932388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917116</t>
+          <t>956610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42743</t>
+          <t>45621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>46962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>70815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83030</t>
+          <t>88771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67946</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101266</t>
+          <t>107928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505792</t>
+          <t>589407</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493595</t>
+          <t>575216</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515385</t>
+          <t>599724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>539517</t>
+          <t>565852</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526547</t>
+          <t>552378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>554816</t>
+          <t>576231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1045310</t>
+          <t>1155258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1027074</t>
+          <t>1136101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1060394</t>
+          <t>1170451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92820</t>
+          <t>83384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105388</t>
+          <t>107483</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85410</t>
+          <t>92610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>122952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>165909</t>
+          <t>172777</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100968</t>
+          <t>149393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207135</t>
+          <t>197204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>827265</t>
+          <t>635323</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794966</t>
+          <t>617233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>861830</t>
+          <t>649553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>607493</t>
+          <t>629403</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588174</t>
+          <t>613934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627471</t>
+          <t>644276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1434758</t>
+          <t>1264727</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393532</t>
+          <t>1240300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1499699</t>
+          <t>1288111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67729</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>58044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82292</t>
+          <t>88206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>137397</t>
+          <t>152631</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123048</t>
+          <t>136197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154551</t>
+          <t>170478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>205127</t>
+          <t>224950</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183783</t>
+          <t>202452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226382</t>
+          <t>248700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>493505</t>
+          <t>537027</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478942</t>
+          <t>521140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506442</t>
+          <t>551302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>410508</t>
+          <t>456224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393354</t>
+          <t>438377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424857</t>
+          <t>472658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>904012</t>
+          <t>993252</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>882757</t>
+          <t>969502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925356</t>
+          <t>1015750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54831</t>
+          <t>58624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>113038</t>
+          <t>125319</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48393</t>
+          <t>111867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176921</t>
+          <t>139822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158148</t>
+          <t>173592</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79752</t>
+          <t>157318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208967</t>
+          <t>192424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>323056</t>
+          <t>358807</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313334</t>
+          <t>348456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333682</t>
+          <t>369724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>495330</t>
+          <t>313847</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>431447</t>
+          <t>299344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>559975</t>
+          <t>327299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>818385</t>
+          <t>672654</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>767566</t>
+          <t>653822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>896781</t>
+          <t>688928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64938</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53923</t>
+          <t>59079</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>84455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>158365</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145164</t>
+          <t>158645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>188235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>223303</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205332</t>
+          <t>226569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241399</t>
+          <t>266215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>217821</t>
+          <t>239567</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206494</t>
+          <t>225743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228836</t>
+          <t>251119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>267466</t>
+          <t>291537</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>253015</t>
+          <t>276374</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>280667</t>
+          <t>305964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>485287</t>
+          <t>531103</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>467191</t>
+          <t>508592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>503258</t>
+          <t>548238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>222400</t>
+          <t>270968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>339187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>490632</t>
+          <t>613414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>660644</t>
+          <t>689803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>760517</t>
+          <t>906063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>961645</t>
+          <t>1009350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3177215</t>
+          <t>3227451</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3139018</t>
+          <t>3193575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3237417</t>
+          <t>3261794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3110238</t>
+          <t>3084482</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3051636</t>
+          <t>3047151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3221648</t>
+          <t>3123540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6287453</t>
+          <t>6311933</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6210452</t>
+          <t>6260366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6411580</t>
+          <t>6363653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
